--- a/RISK MANAGEMENT/Risk Register & Analysis.xlsx
+++ b/RISK MANAGEMENT/Risk Register & Analysis.xlsx
@@ -170,46 +170,10 @@
     <t xml:space="preserve">Dos/Ddos, Social Engineering </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Use of cryptography, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">User end point devices, Secure authentication, Logging, Monitoring activities, </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Email Policy, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">cryptography Policy, </t>
-    </r>
+    <t xml:space="preserve">Use of cryptography, User end point devices, Secure authentication, Logging, Monitoring activities, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email Policy, cryptography Policy, </t>
   </si>
   <si>
     <t xml:space="preserve">R-08</t>
@@ -228,7 +192,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -272,12 +236,6 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -336,7 +294,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -369,15 +327,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -879,13 +829,13 @@
         <f aca="false">F9*G9</f>
         <v>25</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="5" t="s">
         <v>15</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="4" t="s">
         <v>49</v>
       </c>
       <c r="L9" s="6" t="s">
@@ -947,290 +897,290 @@
       <c r="L12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="12"/>
-      <c r="J13" s="12"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="11"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="11"/>
+      <c r="L13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="11"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="11"/>
+      <c r="L14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="14"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="12"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="13"/>
-      <c r="L16" s="11"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="10"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="11"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="11"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="11"/>
+      <c r="L18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="14"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="11"/>
+      <c r="L19" s="12"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12"/>
-      <c r="J20" s="12"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="11"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="12"/>
-      <c r="J21" s="12"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="11"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="11"/>
+      <c r="L21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="12"/>
-      <c r="J22" s="12"/>
-      <c r="K22" s="13"/>
-      <c r="L22" s="11"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="11"/>
+      <c r="L22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="11"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
-      <c r="K23" s="13"/>
-      <c r="L23" s="14"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="11"/>
+      <c r="L23" s="12"/>
     </row>
     <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11"/>
-      <c r="G24" s="11"/>
-      <c r="H24" s="11"/>
-      <c r="I24" s="11"/>
-      <c r="J24" s="11"/>
-      <c r="K24" s="11"/>
-      <c r="L24" s="11"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="11"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
-      <c r="F25" s="11"/>
-      <c r="G25" s="11"/>
-      <c r="H25" s="11"/>
-      <c r="I25" s="11"/>
-      <c r="J25" s="11"/>
-      <c r="K25" s="11"/>
-      <c r="L25" s="11"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="11"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="11"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11"/>
-      <c r="F27" s="11"/>
-      <c r="G27" s="11"/>
-      <c r="H27" s="11"/>
-      <c r="I27" s="11"/>
-      <c r="J27" s="11"/>
-      <c r="K27" s="11"/>
-      <c r="L27" s="11"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-      <c r="L28" s="11"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="11"/>
-      <c r="C29" s="11"/>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11"/>
-      <c r="F29" s="11"/>
-      <c r="G29" s="11"/>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="11"/>
-      <c r="L29" s="11"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="11"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11"/>
-      <c r="F31" s="11"/>
-      <c r="G31" s="11"/>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
-      <c r="K31" s="11"/>
-      <c r="L31" s="11"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-      <c r="L32" s="11"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="11"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-      <c r="L34" s="11"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
